--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h0.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h0.xlsx
@@ -459,31 +459,31 @@
         <v>0.4499999999999886</v>
       </c>
       <c r="D2">
-        <v>0.5320219819094892</v>
+        <v>0.4047808753802802</v>
       </c>
       <c r="E2">
         <v>0.1839449541284232</v>
       </c>
       <c r="F2">
-        <v>0.2659669360379238</v>
+        <v>0.1387258295087148</v>
       </c>
       <c r="G2">
-        <v>-0.08202198190950066</v>
+        <v>0.0452191246197084</v>
       </c>
       <c r="H2">
-        <v>0.08202198190950066</v>
+        <v>-0.0452191246197084</v>
       </c>
       <c r="I2">
-        <v>0.03690266491609336</v>
+        <v>-0.0145908903764267</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -497,22 +497,22 @@
         <v>-0.3499999999999943</v>
       </c>
       <c r="D3">
-        <v>0.5229656037511492</v>
+        <v>0.4784740695367412</v>
       </c>
       <c r="E3">
         <v>0.1457634757526623</v>
       </c>
       <c r="F3">
-        <v>1.018729079503806</v>
+        <v>0.9742375452893979</v>
       </c>
       <c r="G3">
-        <v>-0.8729656037511435</v>
+        <v>-0.8284740695367355</v>
       </c>
       <c r="H3">
-        <v>0.8729656037511435</v>
+        <v>0.8284740695367356</v>
       </c>
       <c r="I3">
-        <v>1.016561946563175</v>
+        <v>0.9278918037880146</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -535,22 +535,22 @@
         <v>-0.8999999999999915</v>
       </c>
       <c r="D4">
-        <v>0.5335276996450126</v>
+        <v>0.1515254269567554</v>
       </c>
       <c r="E4">
         <v>1.20794112302382</v>
       </c>
       <c r="F4">
-        <v>2.641468822668824</v>
+        <v>2.259466549980567</v>
       </c>
       <c r="G4">
-        <v>-1.433527699645004</v>
+        <v>-1.051525426956747</v>
       </c>
       <c r="H4">
-        <v>1.433527699645004</v>
+        <v>1.051525426956747</v>
       </c>
       <c r="I4">
-        <v>5.518235784439376</v>
+        <v>3.646067333789038</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -573,31 +573,31 @@
         <v>-0.7000000000000171</v>
       </c>
       <c r="D5">
-        <v>-0.09703811524846598</v>
+        <v>-3.209643609385049</v>
       </c>
       <c r="E5">
         <v>-1.017521408640446</v>
       </c>
       <c r="F5">
-        <v>-0.4145595238888954</v>
+        <v>-3.527165018025478</v>
       </c>
       <c r="G5">
-        <v>-0.6029618847515511</v>
+        <v>2.509643609385032</v>
       </c>
       <c r="H5">
-        <v>-0.6029618847515511</v>
+        <v>2.509643609385032</v>
       </c>
       <c r="I5">
-        <v>-0.8634902181946508</v>
+        <v>11.40554324734103</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -611,31 +611,31 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D6">
-        <v>0.5024981423644616</v>
+        <v>0.4395909147248004</v>
       </c>
       <c r="E6">
         <v>0.4904915850527526</v>
       </c>
       <c r="F6">
-        <v>0.4929897274172284</v>
+        <v>0.4300824997775672</v>
       </c>
       <c r="G6">
-        <v>-0.002498142364475764</v>
+        <v>0.0604090852751854</v>
       </c>
       <c r="H6">
-        <v>0.002498142364475764</v>
+        <v>-0.0604090852751854</v>
       </c>
       <c r="I6">
-        <v>0.002456876331351499</v>
+        <v>-0.05561103839264053</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -649,22 +649,22 @@
         <v>1.099999999999994</v>
       </c>
       <c r="D7">
-        <v>0.4444015301575642</v>
+        <v>0.1920931682409845</v>
       </c>
       <c r="E7">
         <v>-1.082091798344633</v>
       </c>
       <c r="F7">
-        <v>-1.737690268187063</v>
+        <v>-1.989998630103643</v>
       </c>
       <c r="G7">
-        <v>0.65559846984243</v>
+        <v>0.9079068317590095</v>
       </c>
       <c r="H7">
-        <v>0.65559846984243</v>
+        <v>0.9079068317590095</v>
       </c>
       <c r="I7">
-        <v>1.848644808107305</v>
+        <v>2.789171887769652</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -687,22 +687,22 @@
         <v>0.8</v>
       </c>
       <c r="D8">
-        <v>0.5984434428180319</v>
+        <v>0.5278817260644753</v>
       </c>
       <c r="E8">
         <v>0.4352029183766609</v>
       </c>
       <c r="F8">
-        <v>0.2336463611946927</v>
+        <v>0.1630846444411361</v>
       </c>
       <c r="G8">
-        <v>0.2015565571819682</v>
+        <v>0.2721182739355248</v>
       </c>
       <c r="H8">
-        <v>-0.2015565571819682</v>
+        <v>-0.2721182739355248</v>
       </c>
       <c r="I8">
-        <v>-0.1348109580640418</v>
+        <v>-0.1628049789110708</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -725,22 +725,22 @@
         <v>0.4</v>
       </c>
       <c r="D9">
-        <v>0.5698310446372115</v>
+        <v>0.8158350159267664</v>
       </c>
       <c r="E9">
         <v>0.280777696258258</v>
       </c>
       <c r="F9">
-        <v>0.4506087408954694</v>
+        <v>0.6966127121850244</v>
       </c>
       <c r="G9">
-        <v>-0.1698310446372114</v>
+        <v>-0.4158350159267664</v>
       </c>
       <c r="H9">
-        <v>0.1698310446372114</v>
+        <v>0.4158350159267664</v>
       </c>
       <c r="I9">
-        <v>0.1242121226553057</v>
+        <v>0.4064331560616811</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -763,22 +763,22 @@
         <v>-0.2</v>
       </c>
       <c r="D10">
-        <v>0.4888361074519135</v>
+        <v>0.4070688708672613</v>
       </c>
       <c r="E10">
         <v>-0.01813221787760042</v>
       </c>
       <c r="F10">
-        <v>0.6707038895743132</v>
+        <v>0.5889366529896609</v>
       </c>
       <c r="G10">
-        <v>-0.6888361074519136</v>
+        <v>-0.6070688708672614</v>
       </c>
       <c r="H10">
-        <v>0.6525716716967127</v>
+        <v>0.5708044351120605</v>
       </c>
       <c r="I10">
-        <v>0.4495149301649516</v>
+        <v>0.3465176039095035</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -801,22 +801,22 @@
         <v>0.1</v>
       </c>
       <c r="D11">
-        <v>0.4640669336751295</v>
+        <v>0.4060566115363017</v>
       </c>
       <c r="E11">
         <v>-0.1707092582566427</v>
       </c>
       <c r="F11">
-        <v>0.1933576754184868</v>
+        <v>0.135347353279659</v>
       </c>
       <c r="G11">
-        <v>-0.3640669336751295</v>
+        <v>-0.3060566115363017</v>
       </c>
       <c r="H11">
-        <v>0.0226484171618441</v>
+        <v>-0.03536190497698374</v>
       </c>
       <c r="I11">
-        <v>0.008245539788707762</v>
+        <v>-0.01082274481472432</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -825,7 +825,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -839,22 +839,22 @@
         <v>-0.3</v>
       </c>
       <c r="D12">
-        <v>0.4589753847598654</v>
+        <v>0.2658412787400625</v>
       </c>
       <c r="E12">
         <v>0.2925127928898435</v>
       </c>
       <c r="F12">
-        <v>1.051488177649709</v>
+        <v>0.8583540716299061</v>
       </c>
       <c r="G12">
-        <v>-0.7589753847598654</v>
+        <v>-0.5658412787400625</v>
       </c>
       <c r="H12">
-        <v>0.7589753847598655</v>
+        <v>0.5658412787400626</v>
       </c>
       <c r="I12">
-        <v>1.020063653732889</v>
+        <v>0.6512079782794215</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -877,22 +877,22 @@
         <v>0.8999999999999915</v>
       </c>
       <c r="D13">
-        <v>0.3811469122973433</v>
+        <v>0.1668148420067005</v>
       </c>
       <c r="E13">
         <v>0.1785643430426489</v>
       </c>
       <c r="F13">
-        <v>-0.3402887446599993</v>
+        <v>-0.5546208149506421</v>
       </c>
       <c r="G13">
-        <v>0.5188530877026482</v>
+        <v>0.733185157993291</v>
       </c>
       <c r="H13">
-        <v>0.1617244016173504</v>
+        <v>0.3760564719079932</v>
       </c>
       <c r="I13">
-        <v>0.08391120513602537</v>
+        <v>0.2757190237702615</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -915,31 +915,31 @@
         <v>0.3</v>
       </c>
       <c r="D14">
-        <v>0.4852206541758703</v>
+        <v>0.3071481657186778</v>
       </c>
       <c r="E14">
         <v>-0.0837572512271369</v>
       </c>
       <c r="F14">
-        <v>0.1014634029487334</v>
+        <v>-0.07660908550845907</v>
       </c>
       <c r="G14">
-        <v>-0.1852206541758703</v>
+        <v>-0.007148165718677824</v>
       </c>
       <c r="H14">
-        <v>0.01770615172159651</v>
+        <v>-0.007148165718677824</v>
       </c>
       <c r="I14">
-        <v>0.003279545004811317</v>
+        <v>-0.001146325150683331</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -953,22 +953,22 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D15">
-        <v>0.5129871263628406</v>
+        <v>0.5498874657267171</v>
       </c>
       <c r="E15">
         <v>0.4608782057348194</v>
       </c>
       <c r="F15">
-        <v>0.6738653320976771</v>
+        <v>0.7107656714615536</v>
       </c>
       <c r="G15">
-        <v>-0.2129871263628577</v>
+        <v>-0.2498874657267342</v>
       </c>
       <c r="H15">
-        <v>0.2129871263628577</v>
+        <v>0.2498874657267341</v>
       </c>
       <c r="I15">
-        <v>0.2416857652817661</v>
+        <v>0.2927791192068466</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -991,31 +991,31 @@
         <v>0.2000000000000028</v>
       </c>
       <c r="D16">
-        <v>0.3987129603527378</v>
+        <v>0.1736804633958236</v>
       </c>
       <c r="E16">
         <v>-0.4996974281391754</v>
       </c>
       <c r="F16">
-        <v>-0.3009844677864404</v>
+        <v>-0.5260169647433546</v>
       </c>
       <c r="G16">
-        <v>-0.198712960352735</v>
+        <v>0.02631953660417918</v>
       </c>
       <c r="H16">
-        <v>-0.198712960352735</v>
+        <v>0.02631953660417913</v>
       </c>
       <c r="I16">
-        <v>-0.1591058698402196</v>
+        <v>0.02699632750890513</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1029,25 +1029,25 @@
         <v>0.6200000000000045</v>
       </c>
       <c r="D17">
-        <v>0.4704147728506033</v>
+        <v>0.3086271608792364</v>
       </c>
       <c r="E17">
         <v>0.1813625758282837</v>
       </c>
       <c r="F17">
-        <v>0.03177734867888249</v>
+        <v>-0.1300102632924844</v>
       </c>
       <c r="G17">
-        <v>0.1495852271494013</v>
+        <v>0.3113728391207681</v>
       </c>
       <c r="H17">
-        <v>-0.1495852271494013</v>
+        <v>-0.05135231253579936</v>
       </c>
       <c r="I17">
-        <v>-0.0318825840220107</v>
+        <v>-0.01598971534968886</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -1067,22 +1067,22 @@
         <v>0.4699999999999989</v>
       </c>
       <c r="D18">
-        <v>0.45960676335203</v>
+        <v>0.3194721332081325</v>
       </c>
       <c r="E18">
         <v>0.2013073288242442</v>
       </c>
       <c r="F18">
-        <v>0.1909140921762753</v>
+        <v>0.05077946203237782</v>
       </c>
       <c r="G18">
-        <v>0.01039323664796893</v>
+        <v>0.1505278667918664</v>
       </c>
       <c r="H18">
-        <v>-0.01039323664796893</v>
+        <v>-0.1505278667918664</v>
       </c>
       <c r="I18">
-        <v>-0.004076450046861045</v>
+        <v>-0.03794608687405469</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -1105,22 +1105,22 @@
         <v>0.3400000000000034</v>
       </c>
       <c r="D19">
-        <v>0.4866309068941742</v>
+        <v>0.4935538258476527</v>
       </c>
       <c r="E19">
         <v>-0.07125936757448281</v>
       </c>
       <c r="F19">
-        <v>0.07537153931968799</v>
+        <v>0.0822944582731665</v>
       </c>
       <c r="G19">
-        <v>-0.1466309068941708</v>
+        <v>-0.1535538258476493</v>
       </c>
       <c r="H19">
-        <v>0.004112171745205173</v>
+        <v>0.01103509069868369</v>
       </c>
       <c r="I19">
-        <v>0.0006029714723040196</v>
+        <v>0.00169448039535869</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -1143,31 +1143,31 @@
         <v>0.4499999999999886</v>
       </c>
       <c r="D20">
-        <v>0.4459418294680377</v>
+        <v>0.2854538301566019</v>
       </c>
       <c r="E20">
         <v>0.02307657371240679</v>
       </c>
       <c r="F20">
-        <v>0.01901840318045589</v>
+        <v>-0.1414695961309799</v>
       </c>
       <c r="G20">
-        <v>0.0040581705319509</v>
+        <v>0.1645461698433867</v>
       </c>
       <c r="H20">
-        <v>-0.0040581705319509</v>
+        <v>0.1183930224185731</v>
       </c>
       <c r="I20">
-        <v>-0.0001708285947697693</v>
+        <v>0.01948111837515841</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1181,22 +1181,22 @@
         <v>0.6999999999999886</v>
       </c>
       <c r="D21">
-        <v>0.4898183955613777</v>
+        <v>0.4880370991768954</v>
       </c>
       <c r="E21">
         <v>0.0835432859823011</v>
       </c>
       <c r="F21">
-        <v>-0.1266383184563099</v>
+        <v>-0.1284196148407921</v>
       </c>
       <c r="G21">
-        <v>0.2101816044386109</v>
+        <v>0.2119629008230932</v>
       </c>
       <c r="H21">
-        <v>0.04309503247400875</v>
+        <v>0.04487632885849102</v>
       </c>
       <c r="I21">
-        <v>0.009057783068721202</v>
+        <v>0.00951211684313685</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -1219,31 +1219,31 @@
         <v>0.5500000000000114</v>
       </c>
       <c r="D22">
-        <v>0.5308500955697427</v>
+        <v>0.5892375486112547</v>
       </c>
       <c r="E22">
         <v>-0.05696692470090148</v>
       </c>
       <c r="F22">
-        <v>-0.07611682913117013</v>
+        <v>-0.01772937608965819</v>
       </c>
       <c r="G22">
-        <v>0.01914990443026865</v>
+        <v>-0.03923754861124329</v>
       </c>
       <c r="H22">
-        <v>0.01914990443026865</v>
+        <v>-0.03923754861124329</v>
       </c>
       <c r="I22">
-        <v>0.00254854116710557</v>
+        <v>-0.002930899733349635</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1257,22 +1257,22 @@
         <v>0.6999999999999886</v>
       </c>
       <c r="D23">
-        <v>0.5146509551248899</v>
+        <v>0.498268675818354</v>
       </c>
       <c r="E23">
         <v>0.4027192445571373</v>
       </c>
       <c r="F23">
-        <v>0.2173701996820385</v>
+        <v>0.2009879203755026</v>
       </c>
       <c r="G23">
-        <v>0.1853490448750987</v>
+        <v>0.2017313241816346</v>
       </c>
       <c r="H23">
-        <v>-0.1853490448750987</v>
+        <v>-0.2017313241816346</v>
       </c>
       <c r="I23">
-        <v>-0.114932986226862</v>
+        <v>-0.1217866457998019</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -1295,25 +1295,25 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D24">
-        <v>0.4741444152223665</v>
+        <v>0.3409278159840826</v>
       </c>
       <c r="E24">
         <v>-0.1515848892748725</v>
       </c>
       <c r="F24">
-        <v>0.02255952594751109</v>
+        <v>-0.1106570732907728</v>
       </c>
       <c r="G24">
-        <v>-0.1741444152223836</v>
+        <v>-0.04092781598409972</v>
       </c>
       <c r="H24">
-        <v>-0.1290253633273614</v>
+        <v>-0.04092781598409972</v>
       </c>
       <c r="I24">
-        <v>-0.02246904644549893</v>
+        <v>-0.0107329907871959</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -1333,22 +1333,22 @@
         <v>0.4999999999999716</v>
       </c>
       <c r="D25">
-        <v>0.4777870639207178</v>
+        <v>0.3924672903298065</v>
       </c>
       <c r="E25">
         <v>0.6988415319442993</v>
       </c>
       <c r="F25">
-        <v>0.6766285958650455</v>
+        <v>0.5913088222741343</v>
       </c>
       <c r="G25">
-        <v>0.02221293607925379</v>
+        <v>0.1075327096701651</v>
       </c>
       <c r="H25">
-        <v>-0.02221293607925379</v>
+        <v>-0.107532709670165</v>
       </c>
       <c r="I25">
-        <v>-0.03055323002795202</v>
+        <v>-0.1387333634710314</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
@@ -1371,31 +1371,31 @@
         <v>0.2</v>
       </c>
       <c r="D26">
-        <v>0.4138185309876257</v>
+        <v>0.1122805722851697</v>
       </c>
       <c r="E26">
         <v>0.1826764833261187</v>
       </c>
       <c r="F26">
-        <v>0.3964950143137443</v>
+        <v>0.09495705561128835</v>
       </c>
       <c r="G26">
-        <v>-0.2138185309876257</v>
+        <v>0.08771942771483031</v>
       </c>
       <c r="H26">
-        <v>0.2138185309876257</v>
+        <v>-0.08771942771483031</v>
       </c>
       <c r="I26">
-        <v>0.1238375988152586</v>
+        <v>-0.0243538551500324</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1409,22 +1409,22 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="D27">
-        <v>0.3953020579267524</v>
+        <v>0.1844683999603099</v>
       </c>
       <c r="E27">
         <v>-0.3243526457088434</v>
       </c>
       <c r="F27">
-        <v>-0.0290505877820853</v>
+        <v>-0.2398842457485278</v>
       </c>
       <c r="G27">
-        <v>-0.2953020579267581</v>
+        <v>-0.08446839996031558</v>
       </c>
       <c r="H27">
-        <v>-0.2953020579267581</v>
+        <v>-0.08446839996031558</v>
       </c>
       <c r="I27">
-        <v>-0.1043607021278418</v>
+        <v>-0.04766018741998639</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -1447,22 +1447,22 @@
         <v>-0.1</v>
       </c>
       <c r="D28">
-        <v>0.4494494662203161</v>
+        <v>0.3627307324263691</v>
       </c>
       <c r="E28">
         <v>-0.02531042853141789</v>
       </c>
       <c r="F28">
-        <v>0.5241390376888982</v>
+        <v>0.4374203038949512</v>
       </c>
       <c r="G28">
-        <v>-0.5494494662203161</v>
+        <v>-0.4627307324263691</v>
       </c>
       <c r="H28">
-        <v>0.4988286091574803</v>
+        <v>0.4121098753635333</v>
       </c>
       <c r="I28">
-        <v>0.2740811130370003</v>
+        <v>0.1906959044671075</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -1485,22 +1485,22 @@
         <v>-0.09999999999999432</v>
       </c>
       <c r="D29">
-        <v>0.429419799243115</v>
+        <v>0.1794263626245832</v>
       </c>
       <c r="E29">
         <v>-0.1841593416869248</v>
       </c>
       <c r="F29">
-        <v>0.3452604575561846</v>
+        <v>0.09526702093765275</v>
       </c>
       <c r="G29">
-        <v>-0.5294197992431093</v>
+        <v>-0.2794263626245775</v>
       </c>
       <c r="H29">
-        <v>0.1611011158692598</v>
+        <v>-0.08889232074927202</v>
       </c>
       <c r="I29">
-        <v>0.0852901204213444</v>
+        <v>-0.02483885785222634</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="L29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1523,22 +1523,22 @@
         <v>0.08000000000004093</v>
       </c>
       <c r="D30">
-        <v>0.3825808826190411</v>
+        <v>0.1814061084957765</v>
       </c>
       <c r="E30">
         <v>0.05200447928335454</v>
       </c>
       <c r="F30">
-        <v>0.3545853619023547</v>
+        <v>0.1534105877790901</v>
       </c>
       <c r="G30">
-        <v>-0.3025808826190002</v>
+        <v>-0.1014061084957356</v>
       </c>
       <c r="H30">
-        <v>0.3025808826190002</v>
+        <v>0.1014061084957356</v>
       </c>
       <c r="I30">
-        <v>0.123026313009891</v>
+        <v>0.02083034257719306</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
@@ -1561,22 +1561,22 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="D31">
-        <v>0.4158212270970915</v>
+        <v>0.1900831754885381</v>
       </c>
       <c r="E31">
         <v>2.3218073188947</v>
       </c>
       <c r="F31">
-        <v>2.637628545991797</v>
+        <v>2.411890494383244</v>
       </c>
       <c r="G31">
-        <v>-0.3158212270970972</v>
+        <v>-0.09008317548854378</v>
       </c>
       <c r="H31">
-        <v>0.3158212270970973</v>
+        <v>0.09008317548854361</v>
       </c>
       <c r="I31">
-        <v>1.566295120557808</v>
+        <v>0.4264265308232522</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -1599,22 +1599,22 @@
         <v>-11.9</v>
       </c>
       <c r="D32">
-        <v>0.1862656172266596</v>
+        <v>-0.6845717329199352</v>
       </c>
       <c r="E32">
         <v>-2.209042350248001</v>
       </c>
       <c r="F32">
-        <v>9.877223266978659</v>
+        <v>9.006385916832064</v>
       </c>
       <c r="G32">
-        <v>-12.08626561722666</v>
+        <v>-11.21542826708007</v>
       </c>
       <c r="H32">
-        <v>7.668180916730657</v>
+        <v>6.797343566584063</v>
       </c>
       <c r="I32">
-        <v>92.67967136055535</v>
+        <v>76.23511917772173</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
@@ -1637,22 +1637,22 @@
         <v>6.640000000000001</v>
       </c>
       <c r="D33">
-        <v>-1.982134026001563</v>
+        <v>-7.463655357282573</v>
       </c>
       <c r="E33">
         <v>-1.840304150385469</v>
       </c>
       <c r="F33">
-        <v>-10.46243817638703</v>
+        <v>-15.94395950766804</v>
       </c>
       <c r="G33">
-        <v>8.622134026001564</v>
+        <v>14.10365535728257</v>
       </c>
       <c r="H33">
-        <v>8.622134026001563</v>
+        <v>14.10365535728257</v>
       </c>
       <c r="I33">
-        <v>106.0758932287948</v>
+        <v>250.8231254162322</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -1675,22 +1675,22 @@
         <v>-0.4000000000000057</v>
       </c>
       <c r="D34">
-        <v>-1.488840052368066</v>
+        <v>-4.144592182330832</v>
       </c>
       <c r="E34">
         <v>-0.7406326034063262</v>
       </c>
       <c r="F34">
-        <v>-1.829472655774387</v>
+        <v>-4.485224785737152</v>
       </c>
       <c r="G34">
-        <v>1.08884005236806</v>
+        <v>3.744592182330826</v>
       </c>
       <c r="H34">
-        <v>1.08884005236806</v>
+        <v>3.744592182330826</v>
       </c>
       <c r="I34">
-        <v>2.798433544997755</v>
+        <v>19.56870472536245</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -1713,31 +1713,31 @@
         <v>-0.7094799999999992</v>
       </c>
       <c r="D35">
-        <v>0.4888170872567604</v>
+        <v>-0.8877061776737167</v>
       </c>
       <c r="E35">
         <v>1.097457868393073</v>
       </c>
       <c r="F35">
-        <v>2.295754955649832</v>
+        <v>0.9192316907193552</v>
       </c>
       <c r="G35">
-        <v>-1.19829708725676</v>
+        <v>0.1782261776737175</v>
       </c>
       <c r="H35">
-        <v>1.19829708725676</v>
+        <v>-0.1782261776737175</v>
       </c>
       <c r="I35">
-        <v>4.066077043492896</v>
+        <v>-0.3594268716751026</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1751,22 +1751,22 @@
         <v>1.310000000000016</v>
       </c>
       <c r="D36">
-        <v>0.731431855473491</v>
+        <v>0.892999978012982</v>
       </c>
       <c r="E36">
         <v>-0.323092118130242</v>
       </c>
       <c r="F36">
-        <v>-0.901660262656767</v>
+        <v>-0.740092140117276</v>
       </c>
       <c r="G36">
-        <v>0.5785681445265251</v>
+        <v>0.417000021987034</v>
       </c>
       <c r="H36">
-        <v>0.5785681445265251</v>
+        <v>0.417000021987034</v>
       </c>
       <c r="I36">
-        <v>0.708602712456384</v>
+        <v>0.4433478590654834</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -1789,22 +1789,22 @@
         <v>1.52000000000001</v>
       </c>
       <c r="D37">
-        <v>0.4393764117943757</v>
+        <v>0.464029186385135</v>
       </c>
       <c r="E37">
         <v>-0.174266296544449</v>
       </c>
       <c r="F37">
-        <v>-1.254889884750083</v>
+        <v>-1.230237110159324</v>
       </c>
       <c r="G37">
-        <v>1.080623588205634</v>
+        <v>1.055970813614875</v>
       </c>
       <c r="H37">
-        <v>1.080623588205634</v>
+        <v>1.055970813614875</v>
       </c>
       <c r="I37">
-        <v>1.544379880736759</v>
+        <v>1.483114605101847</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -1827,28 +1827,28 @@
         <v>-0.539999999999992</v>
       </c>
       <c r="D38">
-        <v>0.1639891127141883</v>
+        <v>-0.6356350162097709</v>
       </c>
       <c r="E38">
         <v>-0.1928103593881966</v>
       </c>
       <c r="F38">
-        <v>0.5111787533259837</v>
+        <v>-0.2884453755979755</v>
       </c>
       <c r="G38">
-        <v>-0.7039891127141804</v>
+        <v>0.09563501620977888</v>
       </c>
       <c r="H38">
-        <v>0.3183683939377871</v>
+        <v>0.09563501620977888</v>
       </c>
       <c r="I38">
-        <v>0.2241278831645014</v>
+        <v>0.04602490001645162</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="b">
         <v>1</v>
@@ -1865,31 +1865,31 @@
         <v>0.4652855479103435</v>
       </c>
       <c r="D39">
-        <v>0.497856732295311</v>
+        <v>0.3241408423207837</v>
       </c>
       <c r="E39">
         <v>0.2298806514884979</v>
       </c>
       <c r="F39">
-        <v>0.2624518358734654</v>
+        <v>0.08873594589893813</v>
       </c>
       <c r="G39">
-        <v>-0.03257118438496753</v>
+        <v>0.1411447055895598</v>
       </c>
       <c r="H39">
-        <v>0.03257118438496753</v>
+        <v>-0.1411447055895598</v>
       </c>
       <c r="I39">
-        <v>0.01603585222457622</v>
+        <v>-0.04497104583419696</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1903,22 +1903,22 @@
         <v>0.38</v>
       </c>
       <c r="D40">
-        <v>0.5496377906332163</v>
+        <v>0.6660072552246967</v>
       </c>
       <c r="E40">
         <v>0.2402701443875122</v>
       </c>
       <c r="F40">
-        <v>0.4099079350207285</v>
+        <v>0.526277399612209</v>
       </c>
       <c r="G40">
-        <v>-0.1696377906332163</v>
+        <v>-0.2860072552246967</v>
       </c>
       <c r="H40">
-        <v>0.1696377906332163</v>
+        <v>0.2860072552246968</v>
       </c>
       <c r="I40">
-        <v>0.1102947729089618</v>
+        <v>0.2192381590585927</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
@@ -1941,25 +1941,25 @@
         <v>0.04</v>
       </c>
       <c r="D41">
-        <v>0.4929156585266765</v>
+        <v>0.3437767272872988</v>
       </c>
       <c r="E41">
         <v>-0.3601488926112106</v>
       </c>
       <c r="F41">
-        <v>0.0927667659154659</v>
+        <v>-0.05637216532391182</v>
       </c>
       <c r="G41">
-        <v>-0.4529156585266765</v>
+        <v>-0.3037767272872988</v>
       </c>
       <c r="H41">
-        <v>-0.2673821266957447</v>
+        <v>-0.3037767272872988</v>
       </c>
       <c r="I41">
-        <v>-0.1211015519906665</v>
+        <v>-0.1265294038257749</v>
       </c>
       <c r="J41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
@@ -1979,22 +1979,22 @@
         <v>-0.29</v>
       </c>
       <c r="D42">
-        <v>0.4910150553647586</v>
+        <v>0.4120709423816584</v>
       </c>
       <c r="E42">
         <v>0.1453061035472806</v>
       </c>
       <c r="F42">
-        <v>0.9263211589120393</v>
+        <v>0.847377045928939</v>
       </c>
       <c r="G42">
-        <v>-0.7810150553647586</v>
+        <v>-0.7020709423816585</v>
       </c>
       <c r="H42">
-        <v>0.7810150553647586</v>
+        <v>0.7020709423816585</v>
       </c>
       <c r="I42">
-        <v>0.8369570257200505</v>
+        <v>0.6969339942391621</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
@@ -2017,22 +2017,22 @@
         <v>-0.2078779574152918</v>
       </c>
       <c r="D43">
-        <v>0.5994482967366578</v>
+        <v>0.6519408127754134</v>
       </c>
       <c r="E43">
         <v>0.1273487862293673</v>
       </c>
       <c r="F43">
-        <v>0.9346750403813169</v>
+        <v>0.9871675564200725</v>
       </c>
       <c r="G43">
-        <v>-0.8073262541519496</v>
+        <v>-0.8598187701907052</v>
       </c>
       <c r="H43">
-        <v>0.8073262541519496</v>
+        <v>0.8598187701907052</v>
       </c>
       <c r="I43">
-        <v>0.8573997177577233</v>
+        <v>0.9582820710942839</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
@@ -2055,22 +2055,22 @@
         <v>0.1206478331785803</v>
       </c>
       <c r="D44">
-        <v>0.6333318196243403</v>
+        <v>0.8814549586592991</v>
       </c>
       <c r="E44">
         <v>0.1020880707435432</v>
       </c>
       <c r="F44">
-        <v>0.6147720571893032</v>
+        <v>0.862895196224262</v>
       </c>
       <c r="G44">
-        <v>-0.51268398644576</v>
+        <v>-0.7608071254807188</v>
       </c>
       <c r="H44">
-        <v>0.51268398644576</v>
+        <v>0.7608071254807188</v>
       </c>
       <c r="I44">
-        <v>0.3675227081126292</v>
+        <v>0.7341661454787689</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
@@ -2093,22 +2093,22 @@
         <v>-0.18</v>
       </c>
       <c r="D45">
-        <v>0.5452363198887364</v>
+        <v>0.5350086232236873</v>
       </c>
       <c r="E45">
         <v>-0.0503823720025918</v>
       </c>
       <c r="F45">
-        <v>0.6748539478861446</v>
+        <v>0.6646262512210954</v>
       </c>
       <c r="G45">
-        <v>-0.7252363198887364</v>
+        <v>-0.7150086232236872</v>
       </c>
       <c r="H45">
-        <v>0.6244715758835528</v>
+        <v>0.6142438792185037</v>
       </c>
       <c r="I45">
-        <v>0.4528894675689076</v>
+        <v>0.4391896704035991</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
@@ -2131,22 +2131,22 @@
         <v>0.044</v>
       </c>
       <c r="D46">
-        <v>0.5509988879663087</v>
+        <v>0.5007400141027678</v>
       </c>
       <c r="E46">
         <v>0.3310636170015632</v>
       </c>
       <c r="F46">
-        <v>0.8380625049678718</v>
+        <v>0.787803631104331</v>
       </c>
       <c r="G46">
-        <v>-0.5069988879663087</v>
+        <v>-0.4567400141027678</v>
       </c>
       <c r="H46">
-        <v>0.5069988879663087</v>
+        <v>0.4567400141027679</v>
       </c>
       <c r="I46">
-        <v>0.5927456437308665</v>
+        <v>0.5110314426790112</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
@@ -2169,22 +2169,22 @@
         <v>-0.08251004046350374</v>
       </c>
       <c r="D47">
-        <v>0.5767737563214386</v>
+        <v>0.6148977852456914</v>
       </c>
       <c r="E47">
         <v>-0.2961058799880114</v>
       </c>
       <c r="F47">
-        <v>0.363177916796931</v>
+        <v>0.4013019457211838</v>
       </c>
       <c r="G47">
-        <v>-0.6592837967849423</v>
+        <v>-0.6974078257091951</v>
       </c>
       <c r="H47">
-        <v>0.0670720368089196</v>
+        <v>0.1051960657331724</v>
       </c>
       <c r="I47">
-        <v>0.04421950708548393</v>
+        <v>0.07336455947613334</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
@@ -2207,22 +2207,22 @@
         <v>0.2582525219575302</v>
       </c>
       <c r="D48">
-        <v>0.5308012840444406</v>
+        <v>0.5461074682008229</v>
       </c>
       <c r="E48">
         <v>0.3250145629684917</v>
       </c>
       <c r="F48">
-        <v>0.5975633250554021</v>
+        <v>0.6128695092117844</v>
       </c>
       <c r="G48">
-        <v>-0.2725487620869104</v>
+        <v>-0.2878549462432927</v>
       </c>
       <c r="H48">
-        <v>0.2725487620869104</v>
+        <v>0.2878549462432927</v>
       </c>
       <c r="I48">
-        <v>0.2514474613096684</v>
+        <v>0.2699745691798938</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
@@ -2245,22 +2245,22 @@
         <v>-0.04717552522494373</v>
       </c>
       <c r="D49">
-        <v>0.5192370550060136</v>
+        <v>0.3984361203848173</v>
       </c>
       <c r="E49">
         <v>-0.1523883420589938</v>
       </c>
       <c r="F49">
-        <v>0.4140242381719635</v>
+        <v>0.2932233035507672</v>
       </c>
       <c r="G49">
-        <v>-0.5664125802309573</v>
+        <v>-0.445611645609761</v>
       </c>
       <c r="H49">
-        <v>0.2616358961129697</v>
+        <v>0.1408349614917734</v>
       </c>
       <c r="I49">
-        <v>0.1481938629983858</v>
+        <v>0.06275769894973646</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
@@ -2283,22 +2283,22 @@
         <v>0.2142297805489477</v>
       </c>
       <c r="D50">
-        <v>0.5206063595951018</v>
+        <v>0.4733275747052469</v>
       </c>
       <c r="E50">
         <v>0.4148795034612291</v>
       </c>
       <c r="F50">
-        <v>0.7212560825073833</v>
+        <v>0.6739772976175282</v>
       </c>
       <c r="G50">
-        <v>-0.3063765790461541</v>
+        <v>-0.2590977941562992</v>
       </c>
       <c r="H50">
-        <v>0.3063765790461542</v>
+        <v>0.2590977941562991</v>
       </c>
       <c r="I50">
-        <v>0.3480853341616613</v>
+        <v>0.2821203953115902</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
@@ -2321,22 +2321,22 @@
         <v>0.2394371574146135</v>
       </c>
       <c r="D51">
-        <v>0.531764550366899</v>
+        <v>0.4738675049177161</v>
       </c>
       <c r="E51">
         <v>-0.1722430723603913</v>
       </c>
       <c r="F51">
-        <v>0.1200843205918942</v>
+        <v>0.06218727514271133</v>
       </c>
       <c r="G51">
-        <v>-0.2923273929522855</v>
+        <v>-0.2344303475031026</v>
       </c>
       <c r="H51">
-        <v>-0.05215875176849713</v>
+        <v>-0.11005579721768</v>
       </c>
       <c r="I51">
-        <v>-0.01524743192413018</v>
+        <v>-0.02580041878647171</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
@@ -2359,22 +2359,22 @@
         <v>0.04717883418304325</v>
       </c>
       <c r="D52">
-        <v>0.4771990295558996</v>
+        <v>0.3519456421565676</v>
       </c>
       <c r="E52">
         <v>0.32386998960715</v>
       </c>
       <c r="F52">
-        <v>0.7538901849800064</v>
+        <v>0.6286367975806744</v>
       </c>
       <c r="G52">
-        <v>-0.4300201953728564</v>
+        <v>-0.3047668079735243</v>
       </c>
       <c r="H52">
-        <v>0.4300201953728564</v>
+        <v>0.3047668079735244</v>
       </c>
       <c r="I52">
-        <v>0.4634586408410528</v>
+        <v>0.2902924531043503</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
@@ -2397,22 +2397,22 @@
         <v>0.0959495356205764</v>
       </c>
       <c r="D53">
-        <v>0.5174406429343102</v>
+        <v>0.4328090033804217</v>
       </c>
       <c r="E53">
         <v>0.0959495356205764</v>
       </c>
       <c r="F53">
-        <v>0.5174406429343102</v>
+        <v>0.4328090033804217</v>
       </c>
       <c r="G53">
-        <v>-0.4214911073137338</v>
+        <v>-0.3368594677598453</v>
       </c>
       <c r="H53">
-        <v>0.4214911073137338</v>
+        <v>0.3368594677598453</v>
       </c>
       <c r="I53">
-        <v>0.2585385055744681</v>
+        <v>0.1781173200213496</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
